--- a/Bibsam_tidskriftslistor/bibsam_data_jmir.xlsx
+++ b/Bibsam_tidskriftslistor/bibsam_data_jmir.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27531"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://chalmers-my.sharepoint.com/personal/larher_chalmers_se/Documents/Documents/GitHub/oa-tskr/Bibsam_tidskriftslistor/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\larher\Documents\GitHub\oa-tskr\Bibsam_tidskriftslistor\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="8_{A3C9A57E-9095-4F0D-B44B-7008B808570F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{474C7C16-A626-4C76-A331-6A3244D09B48}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96E37278-E169-4236-9C56-364FD3777AE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{9DF91AE9-51C6-438A-9768-449548D5EA17}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{9DF91AE9-51C6-438A-9768-449548D5EA17}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -74,9 +74,6 @@
     <t>Open</t>
   </si>
   <si>
-    <t>CC/BY</t>
-  </si>
-  <si>
     <t>1929-073X</t>
   </si>
   <si>
@@ -336,6 +333,9 @@
   </si>
   <si>
     <t>https://ojphi.jmir.org/</t>
+  </si>
+  <si>
+    <t>CC-BY</t>
   </si>
 </sst>
 </file>
@@ -732,7 +732,7 @@
     <col min="1" max="1" width="9.5703125" customWidth="1"/>
     <col min="2" max="2" width="16.28515625" customWidth="1"/>
     <col min="3" max="3" width="11.7109375" customWidth="1"/>
-    <col min="4" max="4" width="15.42578125" customWidth="1"/>
+    <col min="4" max="4" width="30.42578125" customWidth="1"/>
     <col min="5" max="5" width="13" customWidth="1"/>
     <col min="6" max="6" width="18.5703125" customWidth="1"/>
     <col min="7" max="7" width="19.5703125" customWidth="1"/>
@@ -778,7 +778,7 @@
         <v>11</v>
       </c>
       <c r="G2" t="s">
-        <v>12</v>
+        <v>99</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
@@ -786,19 +786,19 @@
         <v>7</v>
       </c>
       <c r="B3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3" t="s">
         <v>13</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
         <v>14</v>
       </c>
-      <c r="E3" t="s">
-        <v>15</v>
-      </c>
       <c r="F3" t="s">
         <v>11</v>
       </c>
       <c r="G3" t="s">
-        <v>12</v>
+        <v>99</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -806,19 +806,19 @@
         <v>7</v>
       </c>
       <c r="B4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D4" t="s">
         <v>16</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E4" t="s">
         <v>17</v>
       </c>
-      <c r="E4" t="s">
-        <v>18</v>
-      </c>
       <c r="F4" t="s">
         <v>11</v>
       </c>
       <c r="G4" t="s">
-        <v>12</v>
+        <v>99</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
@@ -826,19 +826,19 @@
         <v>7</v>
       </c>
       <c r="B5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" t="s">
         <v>19</v>
       </c>
-      <c r="D5" t="s">
+      <c r="E5" t="s">
         <v>20</v>
       </c>
-      <c r="E5" t="s">
-        <v>21</v>
-      </c>
       <c r="F5" t="s">
         <v>11</v>
       </c>
       <c r="G5" t="s">
-        <v>12</v>
+        <v>99</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
@@ -846,19 +846,19 @@
         <v>7</v>
       </c>
       <c r="B6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D6" t="s">
         <v>22</v>
       </c>
-      <c r="D6" t="s">
+      <c r="E6" t="s">
         <v>23</v>
       </c>
-      <c r="E6" t="s">
-        <v>24</v>
-      </c>
       <c r="F6" t="s">
         <v>11</v>
       </c>
       <c r="G6" t="s">
-        <v>12</v>
+        <v>99</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -866,19 +866,19 @@
         <v>7</v>
       </c>
       <c r="B7" t="s">
+        <v>24</v>
+      </c>
+      <c r="D7" t="s">
         <v>25</v>
       </c>
-      <c r="D7" t="s">
+      <c r="E7" t="s">
         <v>26</v>
       </c>
-      <c r="E7" t="s">
-        <v>27</v>
-      </c>
       <c r="F7" t="s">
         <v>11</v>
       </c>
       <c r="G7" t="s">
-        <v>12</v>
+        <v>99</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -886,19 +886,19 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
+        <v>27</v>
+      </c>
+      <c r="D8" t="s">
         <v>28</v>
       </c>
-      <c r="D8" t="s">
+      <c r="E8" t="s">
         <v>29</v>
       </c>
-      <c r="E8" t="s">
-        <v>30</v>
-      </c>
       <c r="F8" t="s">
         <v>11</v>
       </c>
       <c r="G8" t="s">
-        <v>12</v>
+        <v>99</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -906,19 +906,19 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
+        <v>30</v>
+      </c>
+      <c r="D9" t="s">
         <v>31</v>
       </c>
-      <c r="D9" t="s">
+      <c r="E9" t="s">
         <v>32</v>
       </c>
-      <c r="E9" t="s">
-        <v>33</v>
-      </c>
       <c r="F9" t="s">
         <v>11</v>
       </c>
       <c r="G9" t="s">
-        <v>12</v>
+        <v>99</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -926,19 +926,19 @@
         <v>7</v>
       </c>
       <c r="B10" t="s">
+        <v>33</v>
+      </c>
+      <c r="D10" t="s">
         <v>34</v>
       </c>
-      <c r="D10" t="s">
+      <c r="E10" t="s">
         <v>35</v>
       </c>
-      <c r="E10" t="s">
-        <v>36</v>
-      </c>
       <c r="F10" t="s">
         <v>11</v>
       </c>
       <c r="G10" t="s">
-        <v>12</v>
+        <v>99</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -946,19 +946,19 @@
         <v>7</v>
       </c>
       <c r="B11" t="s">
+        <v>36</v>
+      </c>
+      <c r="D11" t="s">
         <v>37</v>
       </c>
-      <c r="D11" t="s">
+      <c r="E11" t="s">
         <v>38</v>
       </c>
-      <c r="E11" t="s">
-        <v>39</v>
-      </c>
       <c r="F11" t="s">
         <v>11</v>
       </c>
       <c r="G11" t="s">
-        <v>12</v>
+        <v>99</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -966,19 +966,19 @@
         <v>7</v>
       </c>
       <c r="B12" t="s">
+        <v>39</v>
+      </c>
+      <c r="D12" t="s">
         <v>40</v>
       </c>
-      <c r="D12" t="s">
+      <c r="E12" t="s">
         <v>41</v>
       </c>
-      <c r="E12" t="s">
-        <v>42</v>
-      </c>
       <c r="F12" t="s">
         <v>11</v>
       </c>
       <c r="G12" t="s">
-        <v>12</v>
+        <v>99</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
@@ -986,19 +986,19 @@
         <v>7</v>
       </c>
       <c r="B13" t="s">
+        <v>42</v>
+      </c>
+      <c r="D13" t="s">
         <v>43</v>
       </c>
-      <c r="D13" t="s">
+      <c r="E13" t="s">
         <v>44</v>
       </c>
-      <c r="E13" t="s">
-        <v>45</v>
-      </c>
       <c r="F13" t="s">
         <v>11</v>
       </c>
       <c r="G13" t="s">
-        <v>12</v>
+        <v>99</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
@@ -1006,19 +1006,19 @@
         <v>7</v>
       </c>
       <c r="B14" t="s">
+        <v>45</v>
+      </c>
+      <c r="D14" t="s">
         <v>46</v>
       </c>
-      <c r="D14" t="s">
+      <c r="E14" t="s">
         <v>47</v>
       </c>
-      <c r="E14" t="s">
-        <v>48</v>
-      </c>
       <c r="F14" t="s">
         <v>11</v>
       </c>
       <c r="G14" t="s">
-        <v>12</v>
+        <v>99</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -1026,19 +1026,19 @@
         <v>7</v>
       </c>
       <c r="B15" t="s">
+        <v>48</v>
+      </c>
+      <c r="D15" t="s">
         <v>49</v>
       </c>
-      <c r="D15" t="s">
+      <c r="E15" t="s">
         <v>50</v>
       </c>
-      <c r="E15" t="s">
-        <v>51</v>
-      </c>
       <c r="F15" t="s">
         <v>11</v>
       </c>
       <c r="G15" t="s">
-        <v>12</v>
+        <v>99</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
@@ -1046,19 +1046,19 @@
         <v>7</v>
       </c>
       <c r="B16" t="s">
+        <v>51</v>
+      </c>
+      <c r="D16" t="s">
         <v>52</v>
       </c>
-      <c r="D16" t="s">
+      <c r="E16" t="s">
         <v>53</v>
       </c>
-      <c r="E16" t="s">
-        <v>54</v>
-      </c>
       <c r="F16" t="s">
         <v>11</v>
       </c>
       <c r="G16" t="s">
-        <v>12</v>
+        <v>99</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
@@ -1066,19 +1066,19 @@
         <v>7</v>
       </c>
       <c r="B17" t="s">
+        <v>54</v>
+      </c>
+      <c r="D17" t="s">
         <v>55</v>
       </c>
-      <c r="D17" t="s">
+      <c r="E17" t="s">
         <v>56</v>
       </c>
-      <c r="E17" t="s">
-        <v>57</v>
-      </c>
       <c r="F17" t="s">
         <v>11</v>
       </c>
       <c r="G17" t="s">
-        <v>12</v>
+        <v>99</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
@@ -1086,19 +1086,19 @@
         <v>7</v>
       </c>
       <c r="B18" t="s">
+        <v>57</v>
+      </c>
+      <c r="D18" t="s">
         <v>58</v>
       </c>
-      <c r="D18" t="s">
+      <c r="E18" t="s">
         <v>59</v>
       </c>
-      <c r="E18" t="s">
-        <v>60</v>
-      </c>
       <c r="F18" t="s">
         <v>11</v>
       </c>
       <c r="G18" t="s">
-        <v>12</v>
+        <v>99</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
@@ -1106,19 +1106,19 @@
         <v>7</v>
       </c>
       <c r="B19" t="s">
+        <v>60</v>
+      </c>
+      <c r="D19" t="s">
         <v>61</v>
       </c>
-      <c r="D19" t="s">
+      <c r="E19" t="s">
         <v>62</v>
       </c>
-      <c r="E19" t="s">
-        <v>63</v>
-      </c>
       <c r="F19" t="s">
         <v>11</v>
       </c>
       <c r="G19" t="s">
-        <v>12</v>
+        <v>99</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
@@ -1126,19 +1126,19 @@
         <v>7</v>
       </c>
       <c r="B20" t="s">
+        <v>63</v>
+      </c>
+      <c r="D20" t="s">
         <v>64</v>
       </c>
-      <c r="D20" t="s">
+      <c r="E20" t="s">
         <v>65</v>
       </c>
-      <c r="E20" t="s">
-        <v>66</v>
-      </c>
       <c r="F20" t="s">
         <v>11</v>
       </c>
       <c r="G20" t="s">
-        <v>12</v>
+        <v>99</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
@@ -1146,19 +1146,19 @@
         <v>7</v>
       </c>
       <c r="B21" t="s">
+        <v>66</v>
+      </c>
+      <c r="D21" t="s">
         <v>67</v>
       </c>
-      <c r="D21" t="s">
+      <c r="E21" t="s">
         <v>68</v>
       </c>
-      <c r="E21" t="s">
-        <v>69</v>
-      </c>
       <c r="F21" t="s">
         <v>11</v>
       </c>
       <c r="G21" t="s">
-        <v>12</v>
+        <v>99</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
@@ -1166,19 +1166,19 @@
         <v>7</v>
       </c>
       <c r="B22" t="s">
+        <v>69</v>
+      </c>
+      <c r="D22" t="s">
         <v>70</v>
       </c>
-      <c r="D22" t="s">
+      <c r="E22" t="s">
         <v>71</v>
       </c>
-      <c r="E22" t="s">
-        <v>72</v>
-      </c>
       <c r="F22" t="s">
         <v>11</v>
       </c>
       <c r="G22" t="s">
-        <v>12</v>
+        <v>99</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
@@ -1186,19 +1186,19 @@
         <v>7</v>
       </c>
       <c r="B23" t="s">
+        <v>72</v>
+      </c>
+      <c r="D23" t="s">
         <v>73</v>
       </c>
-      <c r="D23" t="s">
+      <c r="E23" t="s">
         <v>74</v>
       </c>
-      <c r="E23" t="s">
-        <v>75</v>
-      </c>
       <c r="F23" t="s">
         <v>11</v>
       </c>
       <c r="G23" t="s">
-        <v>12</v>
+        <v>99</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
@@ -1206,19 +1206,19 @@
         <v>7</v>
       </c>
       <c r="B24" t="s">
+        <v>75</v>
+      </c>
+      <c r="D24" t="s">
         <v>76</v>
       </c>
-      <c r="D24" t="s">
+      <c r="E24" t="s">
         <v>77</v>
       </c>
-      <c r="E24" t="s">
-        <v>78</v>
-      </c>
       <c r="F24" t="s">
         <v>11</v>
       </c>
       <c r="G24" t="s">
-        <v>12</v>
+        <v>99</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
@@ -1226,19 +1226,19 @@
         <v>7</v>
       </c>
       <c r="B25" t="s">
+        <v>78</v>
+      </c>
+      <c r="D25" t="s">
         <v>79</v>
       </c>
-      <c r="D25" t="s">
+      <c r="E25" t="s">
         <v>80</v>
       </c>
-      <c r="E25" t="s">
-        <v>81</v>
-      </c>
       <c r="F25" t="s">
         <v>11</v>
       </c>
       <c r="G25" t="s">
-        <v>12</v>
+        <v>99</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
@@ -1246,19 +1246,19 @@
         <v>7</v>
       </c>
       <c r="B26" t="s">
+        <v>81</v>
+      </c>
+      <c r="D26" t="s">
         <v>82</v>
       </c>
-      <c r="D26" t="s">
+      <c r="E26" t="s">
         <v>83</v>
       </c>
-      <c r="E26" t="s">
-        <v>84</v>
-      </c>
       <c r="F26" t="s">
         <v>11</v>
       </c>
       <c r="G26" t="s">
-        <v>12</v>
+        <v>99</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
@@ -1266,19 +1266,19 @@
         <v>7</v>
       </c>
       <c r="B27" t="s">
+        <v>84</v>
+      </c>
+      <c r="D27" t="s">
         <v>85</v>
       </c>
-      <c r="D27" t="s">
+      <c r="E27" t="s">
         <v>86</v>
       </c>
-      <c r="E27" t="s">
-        <v>87</v>
-      </c>
       <c r="F27" t="s">
         <v>11</v>
       </c>
       <c r="G27" t="s">
-        <v>12</v>
+        <v>99</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
@@ -1286,19 +1286,19 @@
         <v>7</v>
       </c>
       <c r="B28" t="s">
+        <v>87</v>
+      </c>
+      <c r="D28" t="s">
         <v>88</v>
       </c>
-      <c r="D28" t="s">
+      <c r="E28" t="s">
         <v>89</v>
       </c>
-      <c r="E28" t="s">
-        <v>90</v>
-      </c>
       <c r="F28" t="s">
         <v>11</v>
       </c>
       <c r="G28" t="s">
-        <v>12</v>
+        <v>99</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
@@ -1306,19 +1306,19 @@
         <v>7</v>
       </c>
       <c r="B29" t="s">
+        <v>90</v>
+      </c>
+      <c r="D29" t="s">
         <v>91</v>
       </c>
-      <c r="D29" t="s">
+      <c r="E29" t="s">
         <v>92</v>
       </c>
-      <c r="E29" t="s">
-        <v>93</v>
-      </c>
       <c r="F29" t="s">
         <v>11</v>
       </c>
       <c r="G29" t="s">
-        <v>12</v>
+        <v>99</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
@@ -1326,19 +1326,19 @@
         <v>7</v>
       </c>
       <c r="B30" t="s">
+        <v>93</v>
+      </c>
+      <c r="D30" t="s">
         <v>94</v>
       </c>
-      <c r="D30" t="s">
+      <c r="E30" t="s">
         <v>95</v>
       </c>
-      <c r="E30" t="s">
-        <v>96</v>
-      </c>
       <c r="F30" t="s">
         <v>11</v>
       </c>
       <c r="G30" t="s">
-        <v>12</v>
+        <v>99</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
@@ -1346,19 +1346,19 @@
         <v>7</v>
       </c>
       <c r="B31" t="s">
+        <v>96</v>
+      </c>
+      <c r="D31" t="s">
         <v>97</v>
       </c>
-      <c r="D31" t="s">
+      <c r="E31" t="s">
         <v>98</v>
       </c>
-      <c r="E31" t="s">
-        <v>99</v>
-      </c>
       <c r="F31" t="s">
         <v>11</v>
       </c>
       <c r="G31" t="s">
-        <v>12</v>
+        <v>99</v>
       </c>
     </row>
   </sheetData>
